--- a/src/data/coupons.xlsx
+++ b/src/data/coupons.xlsx
@@ -2,21 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4C67D9-BB10-444C-BD56-314B6D4B5998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034612CD-BF73-4096-BF15-C444E2F901E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="96" windowWidth="11808" windowHeight="11076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Coupons" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,69 +39,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Flat Discount</t>
-  </si>
-  <si>
-    <t>Percentage</t>
-  </si>
-  <si>
-    <t>Fixed Price</t>
-  </si>
-  <si>
-    <t>Dealer Only</t>
-  </si>
-  <si>
-    <t>Retail Only</t>
-  </si>
-  <si>
-    <t>Commission</t>
-  </si>
-  <si>
-    <t>Expiry Date</t>
-  </si>
-  <si>
-    <t>Minimum Order Value</t>
-  </si>
-  <si>
-    <t>Usage Limit</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>vikram</t>
-  </si>
-  <si>
-    <t>dealer</t>
-  </si>
-  <si>
-    <t>yes</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Coupon Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Discount Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Discount Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minimum Spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Usage Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Start Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Expiry Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Active</t>
+  </si>
+  <si>
+    <t>SAVE10</t>
+  </si>
+  <si>
+    <t>percentage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +97,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -106,36 +105,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -158,44 +141,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -222,14 +205,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -256,6 +257,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,253 +286,223 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.21875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C2">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>10000</v>
-      </c>
-      <c r="K2">
-        <v>200</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
+        <v>500</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46387</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/data/coupons.xlsx
+++ b/src/data/coupons.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034612CD-BF73-4096-BF15-C444E2F901E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8D37B7-DE94-4A9C-B3A4-0D08A0DF0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,10 +65,10 @@
     <t xml:space="preserve"> Active</t>
   </si>
   <si>
-    <t>SAVE10</t>
-  </si>
-  <si>
     <t>percentage</t>
+  </si>
+  <si>
+    <t>SAVE5</t>
   </si>
 </sst>
 </file>
@@ -449,6 +449,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -478,19 +488,19 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>500</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F2" s="2">
         <v>46023</v>

--- a/src/data/coupons.xlsx
+++ b/src/data/coupons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8D37B7-DE94-4A9C-B3A4-0D08A0DF0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED86427-C22A-4022-A427-0307636FC8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-168" yWindow="408" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,36 +39,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Coupon Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Discount Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Discount Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Minimum Spend</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Usage Limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Start Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Expiry Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Active</t>
-  </si>
-  <si>
-    <t>percentage</t>
-  </si>
-  <si>
-    <t>SAVE5</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+  <si>
+    <t>Coupon Code | Discount Type | Discount Value | Minimum Spend | Usage Limit |</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>Expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELCOME10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Percentage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-01-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-12-31 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> true </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOOLS500 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fixed </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-06-30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLAR2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-02-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARYANA100 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unlimited </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POWERPRO </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-03-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-09-30 </t>
   </si>
 </sst>
 </file>
@@ -112,7 +142,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -460,56 +490,148 @@
     <col min="8" max="8" width="6.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="C2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>500</v>
+      </c>
+      <c r="D3">
+        <v>5000</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>500</v>
-      </c>
-      <c r="E2">
+      <c r="C4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D4">
+        <v>15000</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
         <v>1000</v>
       </c>
-      <c r="F2" s="2">
-        <v>46023</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46387</v>
-      </c>
-      <c r="H2" t="b">
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="D6">
+        <v>10000</v>
+      </c>
+      <c r="E6">
         <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/coupons.xlsx
+++ b/src/data/coupons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED86427-C22A-4022-A427-0307636FC8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4839FE53-4E1B-4783-A411-C6FA04EA2AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-168" yWindow="408" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,73 +39,76 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
-  <si>
-    <t>Coupon Code | Discount Type | Discount Value | Minimum Spend | Usage Limit |</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>|</t>
-  </si>
-  <si>
-    <t>Expiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELCOME10 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Percentage </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-01-01 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-12-31 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> true </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOOLS500 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fixed </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-06-30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOLAR2026 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-02-01 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARYANA100 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Unlimited </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POWERPRO </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-03-01 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026-09-30 </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>discount_type</t>
+  </si>
+  <si>
+    <t>discount_value</t>
+  </si>
+  <si>
+    <t>target_type</t>
+  </si>
+  <si>
+    <t>target_value</t>
+  </si>
+  <si>
+    <t>min_purchase</t>
+  </si>
+  <si>
+    <t>max_discount</t>
+  </si>
+  <si>
+    <t>expiry_date</t>
+  </si>
+  <si>
+    <t>SUMMER20</t>
+  </si>
+  <si>
+    <t>percentage</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>Nike, Puma</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>FLAT50</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>SHOE10</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Footwear</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,9 +117,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,7 +144,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -135,14 +152,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,158 +524,132 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
     <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="15" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>2</v>
-      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+    <row r="2" spans="1:9" ht="15" thickBot="1">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>50</v>
+      </c>
+      <c r="H2" s="5">
+        <v>46265</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:9" ht="15" thickBot="1">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4">
+        <v>200</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5">
+        <v>46387</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>500</v>
-      </c>
-      <c r="D3">
-        <v>5000</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D4">
-        <v>15000</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C4" s="4">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46280</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="D6">
-        <v>10000</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
-      </c>
+      <c r="C6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/data/coupons.xlsx
+++ b/src/data/coupons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4839FE53-4E1B-4783-A411-C6FA04EA2AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DEA88E-0340-45BA-BDFB-010BE739BB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="540" yWindow="1236" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,9 +65,6 @@
     <t>max_discount</t>
   </si>
   <si>
-    <t>expiry_date</t>
-  </si>
-  <si>
     <t>SUMMER20</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>Footwear</t>
+  </si>
+  <si>
+    <t>expiryDate</t>
   </si>
 </sst>
 </file>
@@ -557,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>0</v>
@@ -565,19 +565,19 @@
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="4">
         <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -589,24 +589,24 @@
         <v>46265</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="4">
         <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="F3" s="4">
         <v>200</v>
@@ -616,24 +616,24 @@
         <v>46387</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4">
         <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="F4" s="4">
         <v>30</v>
@@ -645,7 +645,7 @@
         <v>46280</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -653,5 +653,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/data/coupons.xlsx
+++ b/src/data/coupons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DEA88E-0340-45BA-BDFB-010BE739BB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD336BE2-7C4D-45D4-947D-9624168E1BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1236" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="8940" yWindow="924" windowWidth="12996" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>brand</t>
   </si>
   <si>
-    <t>Nike, Puma</t>
-  </si>
-  <si>
     <t>active</t>
   </si>
   <si>
@@ -98,10 +95,13 @@
     <t>category</t>
   </si>
   <si>
-    <t>Footwear</t>
-  </si>
-  <si>
     <t>expiryDate</t>
+  </si>
+  <si>
+    <t>Eastman, JRSDrive</t>
+  </si>
+  <si>
+    <t>Foxcare</t>
   </si>
 </sst>
 </file>
@@ -557,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -589,39 +589,41 @@
         <v>46265</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1">
       <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="4">
         <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="F3" s="4">
         <v>200</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <v>50</v>
+      </c>
       <c r="H3" s="5">
         <v>46387</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>9</v>
@@ -630,10 +632,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4">
         <v>30</v>
@@ -645,7 +647,7 @@
         <v>46280</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
